--- a/data/trans_dic/P21D_6_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,07</t>
+          <t>0,66; 6,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,36</t>
+          <t>0,28; 2,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,43</t>
+          <t>0,66; 3,25</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,62</t>
+          <t>3,64; 9,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,28</t>
+          <t>2,58; 7,26</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,96</t>
+          <t>0,14; 1,9</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,06</t>
+          <t>0,68; 3,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,02</t>
+          <t>0,35; 1,97</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,08</t>
+          <t>0,22; 1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,82</t>
+          <t>0,85; 1,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,24</t>
+          <t>0,59; 1,22</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3072</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3493</t>
+          <t>0; 3338</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1663; 12770</t>
+          <t>1392; 13035</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>592; 5572</t>
+          <t>660; 5436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2700; 15290</t>
+          <t>2956; 14529</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6279</t>
+          <t>0; 7086</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5354; 13998</t>
+          <t>5302; 14234</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6809; 17503</t>
+          <t>6206; 17467</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6648</t>
+          <t>0; 6235</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4017</t>
+          <t>0; 4027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>612; 7595</t>
+          <t>559; 7351</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1002</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1354</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3065</t>
+          <t>0; 2745</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 2136</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2094</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2420; 12445</t>
+          <t>2092; 11614</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2373; 12461</t>
+          <t>2145; 12201</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2762</t>
+          <t>0; 2429</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3072</t>
+          <t>0; 3078</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3352; 17969</t>
+          <t>3735; 17563</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13392; 29039</t>
+          <t>13469; 29134</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19536; 40407</t>
+          <t>19316; 39603</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_6_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,2</t>
+          <t>0,59; 5,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,3</t>
+          <t>0,24; 2,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,25</t>
+          <t>0,68; 3,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,78</t>
+          <t>3,76; 10,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,26</t>
+          <t>2,91; 7,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,9</t>
+          <t>0,18; 2,07</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,79</t>
+          <t>0,7; 3,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,97</t>
+          <t>0,32; 1,83</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,06</t>
+          <t>0,25; 1,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,83</t>
+          <t>0,83; 1,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,22</t>
+          <t>0,66; 1,26</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>985</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>985</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3591</t>
+          <t>0; 2986</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3338</t>
+          <t>0; 3110</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7565</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1392; 13035</t>
+          <t>1313; 12732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>660; 5436</t>
+          <t>611; 6237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2956; 14529</t>
+          <t>3229; 15608</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11081</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7086</t>
+          <t>0; 6886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5302; 14234</t>
+          <t>5496; 14648</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6206; 17467</t>
+          <t>6957; 17325</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2915</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 6638</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4027</t>
+          <t>0; 4062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>559; 7351</t>
+          <t>671; 7800</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2745</t>
+          <t>0; 2143</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2136</t>
+          <t>0; 3025</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5890</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2092; 11614</t>
+          <t>2489; 12522</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2145; 12201</t>
+          <t>2235; 12991</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2429</t>
+          <t>0; 3518</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 3718</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3735; 17563</t>
+          <t>3935; 17198</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13469; 29134</t>
+          <t>14057; 29193</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19316; 39603</t>
+          <t>21586; 40987</t>
         </is>
       </c>
     </row>
